--- a/data/trans_orig/IP13_R1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R1_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112203</t>
+          <t>111545</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135045</t>
+          <t>136124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250224</t>
+          <t>250102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256335</t>
+          <t>256376</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>361</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185474</t>
+          <t>185112</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>190011</t>
+          <t>190002</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>247783</t>
+          <t>247539</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>254672</t>
+          <t>254674</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>436082</t>
+          <t>436132</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>443591</t>
+          <t>443581</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10519</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179066</t>
+          <t>179503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>187888</t>
+          <t>187731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172864</t>
+          <t>173542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182759</t>
+          <t>182844</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356897</t>
+          <t>356805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369318</t>
+          <t>368811</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,82 +1774,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2966</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7515</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>4906</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>10937</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>3,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2966</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7646</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>10451</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162697</t>
+          <t>162566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167962</t>
+          <t>167395</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,82 +1887,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>178272</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>173723</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>180339</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>344295</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>338264</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>347189</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>96,87%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>178272</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>173592</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>180669</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,78%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>344295</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>338750</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>346898</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,47 +2117,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6812</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>19822</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11864</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6848</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>19006</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>15480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>648500</t>
+          <t>648397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>659426</t>
+          <t>659367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,49 +2230,49 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>749384</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>741426</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>754436</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>749384</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>742242</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>754400</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1886</t>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395585</t>
+          <t>1394883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1411857</t>
+          <t>1411108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13_R1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R1_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,22 +795,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124286</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>121638</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>125369</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>115708</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>111545</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>98,66%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>119429</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>115246</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>121071</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>138646</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>136124</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>139689</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>362</t>
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>254354</t>
+          <t>243715</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250102</t>
+          <t>239484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256376</t>
+          <t>245871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125369</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125369</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125369</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139689</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139689</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139689</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>256969</t>
+          <t>246441</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256969</t>
+          <t>246441</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>256969</t>
+          <t>246441</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2178</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5400</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>235028</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>230423</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>236732</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>188472</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>185112</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>190002</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>252795</t>
+          <t>182521</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>247539</t>
+          <t>179325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>254674</t>
+          <t>183734</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>441268</t>
+          <t>417549</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>436132</t>
+          <t>412416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>443581</t>
+          <t>419887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>10705</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>17821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>163001</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>156340</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165936</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,87%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>184558</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>179503</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>187731</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,35%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>179671</t>
+          <t>151031</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173542</t>
+          <t>145499</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182844</t>
+          <t>153856</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>364228</t>
+          <t>314032</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356805</t>
+          <t>306724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>368811</t>
+          <t>318287</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2797</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6954</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>567</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5396</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>489</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>166579</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>162422</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>168474</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>166022</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>162566</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167395</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>178272</t>
+          <t>165314</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173723</t>
+          <t>162281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180339</t>
+          <t>166656</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>344295</t>
+          <t>331893</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>338264</t>
+          <t>327282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347189</t>
+          <t>334772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>688895</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>681246</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>693830</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,28%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>654761</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>648397</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>659367</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>749384</t>
+          <t>618295</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741426</t>
+          <t>610887</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754436</t>
+          <t>622599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1404145</t>
+          <t>1307189</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394883</t>
+          <t>1297430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1411108</t>
+          <t>1314178</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
